--- a/Current_Solution/current_input.xlsx
+++ b/Current_Solution/current_input.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0597404-618D-D14B-8456-3F927E75EE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7843C501-6B8B-A342-BA2C-A93B94EE1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="780" windowWidth="29000" windowHeight="17160" activeTab="1" xr2:uid="{936F0170-C818-8748-95D6-B9EFAFCA5A4F}"/>
   </bookViews>
   <sheets>
-    <sheet name="marsvaktir" sheetId="3" r:id="rId1"/>
-    <sheet name="aprílvaktir" sheetId="4" r:id="rId2"/>
+    <sheet name="03_26" sheetId="3" r:id="rId1"/>
+    <sheet name="04_26" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/Current_Solution/current_input.xlsx
+++ b/Current_Solution/current_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7843C501-6B8B-A342-BA2C-A93B94EE1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEEC8E3-9E1B-6C48-AC53-092C8E29FBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="780" windowWidth="29000" windowHeight="17160" activeTab="1" xr2:uid="{936F0170-C818-8748-95D6-B9EFAFCA5A4F}"/>
+    <workbookView xWindow="300" yWindow="780" windowWidth="29000" windowHeight="17160" xr2:uid="{936F0170-C818-8748-95D6-B9EFAFCA5A4F}"/>
   </bookViews>
   <sheets>
     <sheet name="03_26" sheetId="3" r:id="rId1"/>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CF9BA2-F21A-1244-9B5B-232E4F79D1D2}">
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
@@ -1330,10 +1330,13 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
@@ -1349,13 +1352,13 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
@@ -1369,15 +1372,15 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29">
+        <v>19</v>
+      </c>
+      <c r="C29">
         <v>17</v>
-      </c>
-      <c r="C29">
-        <v>3</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
@@ -1391,15 +1394,12 @@
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
     </row>
-    <row r="30" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30">
-        <v>19</v>
-      </c>
-      <c r="C30">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="31" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="32" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
@@ -1451,12 +1451,12 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
     </row>
-    <row r="33" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
@@ -1472,10 +1472,10 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
@@ -1491,10 +1491,13 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35">
         <v>34</v>
       </c>
-      <c r="B35">
-        <v>12</v>
+      <c r="C35">
+        <v>35</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -1510,13 +1513,10 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36">
-        <v>34</v>
-      </c>
-      <c r="C36">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -1532,10 +1532,13 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>30</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -1551,13 +1554,10 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38">
-        <v>5</v>
-      </c>
-      <c r="C38">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
@@ -1573,10 +1573,13 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39">
-        <v>33</v>
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
@@ -1592,13 +1595,10 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>13</v>
-      </c>
-      <c r="C40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -1614,10 +1614,13 @@
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
@@ -1633,13 +1636,10 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42">
-        <v>32</v>
-      </c>
-      <c r="C42">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -1654,23 +1654,9 @@
       <c r="X42" s="5"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>2</v>
-      </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="J44" s="2"/>
@@ -1766,11 +1752,6 @@
       <c r="J62" s="2"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J63" s="2"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
